--- a/frontend-react/public/data/references_template.xlsx
+++ b/frontend-react/public/data/references_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="13660"/>
+    <workbookView windowWidth="28800" windowHeight="11520"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="95">
   <si>
     <t>Title</t>
   </si>
@@ -59,10 +59,20 @@
     <t>web</t>
   </si>
   <si>
+    <t>Web_Hide</t>
+  </si>
+  <si>
     <t>Fabrication of ovalbumin/κ-carrageenan complex nanoparticles as a novel carrier for curcumin delivery.</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman Bold"/>
+        <charset val="134"/>
+      </rPr>
       <t>Hujun Xie*</t>
     </r>
     <r>
@@ -83,6 +93,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>ESI</t>
     </r>
     <r>
@@ -106,6 +122,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">Chuyue Xiang, Jian Gao, Haoxin Ye, Gerui Ren, Xiangjuan Ma, </t>
     </r>
     <r>
@@ -136,6 +158,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman Bold"/>
+        <charset val="134"/>
+      </rPr>
       <t>Hujun Xie</t>
     </r>
     <r>
@@ -152,13 +181,20 @@
     <t>npj Science of Food</t>
   </si>
   <si>
-    <t>https://doi.org/10.1038/s41538-025-00703-5.</t>
+    <t>https://doi.org/10.1038/s41538-025-00703-5</t>
   </si>
   <si>
     <t>Comparative analysis of carrageenan/ovalbumin and carrageenan oligosaccharide/ovalbumin complexes.</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman Bold"/>
+        <charset val="134"/>
+      </rPr>
       <t>Hujun Xie</t>
     </r>
     <r>
@@ -173,6 +209,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>ESI</t>
     </r>
     <r>
@@ -187,6 +229,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>前</t>
     </r>
     <r>
@@ -207,6 +255,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>Gerui Ren, Ruiqi Hu, Jiajun Mao, Xinpei Cai, Tianrong Wang, Xin Song, Wentao Wu, Caixin Zhuge, Min Huang, </t>
     </r>
     <r>
@@ -240,6 +294,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>Gerui Ren, Ying He, Junfei Lv, Ying Zhu, Zhengfang Xue, Yujing Zhan, Yufan Sun, Xin Luo, Ting Li, Yuling Song, Fuge Niu, Min Huang, Sheng Fang, Linglin Fu, </t>
     </r>
     <r>
@@ -268,6 +328,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>前</t>
     </r>
     <r>
@@ -288,6 +354,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>Hujun Xie</t>
     </r>
     <r>
@@ -308,6 +381,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">Jian Gao, Yuezhong Mao, Chuyue Xiang, Mengna Cao, Gerui Ren, </t>
     </r>
     <r>
@@ -343,6 +422,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">Gerui Ren, Jieyu Shi, Sijie Huang, Chengzhi Liu, Fangfang Ni, Ying He, Xin Luo, Ting Li, Yuling Song, Min Huang, </t>
     </r>
     <r>
@@ -370,6 +455,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">Co-encapsulation of </t>
     </r>
     <r>
@@ -413,6 +504,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>Hujun Xie</t>
     </r>
     <r>
@@ -452,6 +550,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">Rongmi Zhou, Fangfang Ni, Shiyi Wu, Xinyu Wang, Jing Ming, Lantong Zhang, Lijuan Dong, Zhijun Song, Gerui Rena, Min Huang*, Shuangbin Xu, Qiong Zhang, Khaled F. El-Massry, </t>
     </r>
     <r>
@@ -482,6 +586,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">Qingbo Jiao, Haoxin Ye, Nan Lv, Min Huang, Ruibo Wu, Tianxi Yang, Zexing Cao, Qunfang Lei, Wenjun Fang, </t>
     </r>
     <r>
@@ -512,6 +622,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>Tianrong Wang, Tiantian Chen, Jing Ming, Qingbo Jiao, Jiayi Han, Hao Li, Zhijun Song, Gerui Ren, Min Huang, Qunfang Lei, Wenjun Fang, Zexing Cao, Khaled F. El-Massry, </t>
     </r>
     <r>
@@ -544,6 +660,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">Chengzhi Liu, Nan Lv, Yuling Song, Lijuan Dong, Min Huang*, Qing Shen, Gerui Ren, Ruibo Wu, Binju Wang, Zexing Cao, </t>
     </r>
     <r>
@@ -574,6 +696,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>Hujun Xie*</t>
     </r>
     <r>
@@ -594,6 +723,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">Min Huang, Yuling Song, Nan Lv, Chengzhi Liu, Gerui Ren, Qing Shen, Binju Wang, Zexing Cao, </t>
     </r>
     <r>
@@ -624,6 +759,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">Qingbo Jiao, Gerui Ren, Nan Lv, Hao Li, Tianrong Wang, Min Huang*, Ruibo Wu, Zexing Cao, </t>
     </r>
     <r>
@@ -654,6 +795,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">Min Huang*, Jiayi Han, Hao Li, Junhao Lin, Qingbo Jiao, Zexing Cao, Qunfang Lei, Wenjun Fang, Gerui Ren, Zhijun Song, Ying Zheng, Ruibo Wu, </t>
     </r>
     <r>
@@ -690,6 +837,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>Chengzhi Liu, Nan Lv, Gerui Ren, Ruibo Wu, Binju Wang, Zexing Cao,</t>
     </r>
     <r>
@@ -713,6 +866,26 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1%</t>
+    </r>
+  </si>
+  <si>
     <t>https://doi.org/10.1016/j.foodhyd.2021.106906</t>
   </si>
   <si>
@@ -720,7 +893,7 @@
   </si>
   <si>
     <r>
-      <t>Chengzhi Liu, Nan Lv,, Yongquan Xu*, Huafei Tong, Yulu Sun, Min Huang, Gerui Ren, Ruibo Wu, Binju Wang, Zexing Cao, </t>
+      <t>Chengzhi Liu, Nan Lv, Yongquan Xu*, Huafei Tong, Yulu Sun, Min Huang, Gerui Ren, Ruibo Wu, Binju Wang, Zexing Cao, </t>
     </r>
     <r>
       <rPr>
@@ -750,6 +923,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">Min Huang, Yuanru Xu, Hao Li, Qingbo Jiao, Gerui Rena, Zexing Cao, Ruibo Wu, Ying Zheng, Qunfang Lei, Wenjun Fang, </t>
     </r>
     <r>
@@ -776,6 +955,9 @@
     <t>Journal of Physical Chemistry B</t>
   </si>
   <si>
+    <t>https://doi.org/10.1021/acs.jpcb.5c06919</t>
+  </si>
+  <si>
     <t>https://pubs.acs.org/doi/10.1021/acs.jpcb.5c06919</t>
   </si>
   <si>
@@ -783,6 +965,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman Bold"/>
+        <charset val="134"/>
+      </rPr>
       <t>Hujun Xie*</t>
     </r>
     <r>
@@ -815,7 +1004,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -883,13 +1072,6 @@
       <color theme="1"/>
       <name val="宋体-简"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1368,152 +1550,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1530,9 +1712,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify"/>
     </xf>
@@ -1542,12 +1721,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify"/>
     </xf>
@@ -1555,6 +1728,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1903,7 +2079,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="179.923076923077" customWidth="1"/>
@@ -1912,9 +2088,10 @@
     <col min="6" max="6" width="11.7692307692308" customWidth="1"/>
     <col min="8" max="8" width="15.0769230769231" customWidth="1"/>
     <col min="10" max="10" width="75.4423076923077" customWidth="1"/>
+    <col min="11" max="11" width="72.5480769230769" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17" customHeight="1" spans="1:10">
+    <row r="1" ht="17" customHeight="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1945,16 +2122,19 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" s="4">
         <v>2019</v>
@@ -1963,30 +2143,31 @@
         <v>89</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="4">
         <v>12</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="13" t="s">
         <v>16</v>
       </c>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:11">
       <c r="A3" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" s="4">
         <v>2020</v>
@@ -2001,24 +2182,25 @@
         <v>12</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" s="13" t="s">
-        <v>19</v>
+        <v>16</v>
+      </c>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:11">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" s="4">
         <v>2026</v>
@@ -2028,19 +2210,22 @@
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
-      <c r="J4" s="13" t="s">
-        <v>23</v>
+      <c r="J4" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:11">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" s="4">
         <v>2025</v>
@@ -2055,24 +2240,25 @@
         <v>12</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" s="13" t="s">
         <v>28</v>
       </c>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:11">
       <c r="A6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="6" t="s">
         <v>30</v>
       </c>
+      <c r="B6" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="C6" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" s="4">
         <v>2026</v>
@@ -2086,19 +2272,20 @@
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
-      <c r="J6" s="13" t="s">
+      <c r="J6" s="10"/>
+      <c r="K6" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" ht="17" spans="1:11">
+      <c r="A7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="7" ht="17" spans="1:10">
-      <c r="A7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>31</v>
       </c>
       <c r="D7" s="4">
         <v>2023</v>
@@ -2113,24 +2300,25 @@
         <v>9</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="J7" s="13" t="s">
         <v>37</v>
       </c>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:11">
       <c r="A8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="7" t="s">
         <v>39</v>
       </c>
+      <c r="B8" s="6" t="s">
+        <v>40</v>
+      </c>
       <c r="C8" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" s="4">
         <v>2025</v>
@@ -2144,19 +2332,20 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
-      <c r="J8" s="13" t="s">
-        <v>40</v>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="9" ht="17" spans="1:10">
+    <row r="9" ht="17" spans="1:11">
       <c r="A9" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D9" s="4">
         <v>2021</v>
@@ -2171,24 +2360,25 @@
         <v>10</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="J9" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>43</v>
       </c>
       <c r="D10" s="4">
         <v>2022</v>
@@ -2203,24 +2393,25 @@
         <v>9</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="J10" s="13" t="s">
-        <v>47</v>
+        <v>37</v>
+      </c>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:11">
       <c r="A11" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B11" s="9" t="s">
         <v>49</v>
       </c>
+      <c r="B11" s="8" t="s">
+        <v>50</v>
+      </c>
       <c r="C11" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D11" s="4">
         <v>2024</v>
@@ -2235,24 +2426,25 @@
         <v>12</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" s="13" t="s">
-        <v>50</v>
+        <v>16</v>
+      </c>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10" t="s">
+        <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:11">
       <c r="A12" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B12" s="10" t="s">
         <v>52</v>
       </c>
+      <c r="B12" s="5" t="s">
+        <v>53</v>
+      </c>
       <c r="C12" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D12" s="4">
         <v>2025</v>
@@ -2266,19 +2458,20 @@
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
-      <c r="J12" s="13" t="s">
-        <v>53</v>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:11">
       <c r="A13" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B13" s="11" t="s">
         <v>55</v>
       </c>
+      <c r="B13" s="7" t="s">
+        <v>56</v>
+      </c>
       <c r="C13" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" s="4">
         <v>2024</v>
@@ -2292,19 +2485,20 @@
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
-      <c r="J13" s="13" t="s">
-        <v>56</v>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="14" ht="17" spans="1:10">
+    <row r="14" ht="17" spans="1:11">
       <c r="A14" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B14" s="10" t="s">
         <v>58</v>
       </c>
+      <c r="B14" s="5" t="s">
+        <v>59</v>
+      </c>
       <c r="C14" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14" s="4">
         <v>2026</v>
@@ -2318,19 +2512,20 @@
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
       <c r="I14" s="4"/>
-      <c r="J14" s="13" t="s">
-        <v>59</v>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10" t="s">
+        <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:11">
       <c r="A15" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B15" s="10" t="s">
         <v>61</v>
       </c>
+      <c r="B15" s="5" t="s">
+        <v>62</v>
+      </c>
       <c r="C15" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D15" s="4">
         <v>2023</v>
@@ -2345,24 +2540,25 @@
         <v>12</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J15" s="13" t="s">
-        <v>62</v>
+        <v>16</v>
+      </c>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10" t="s">
+        <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:11">
       <c r="A16" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B16" s="9" t="s">
         <v>64</v>
       </c>
+      <c r="B16" s="8" t="s">
+        <v>65</v>
+      </c>
       <c r="C16" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D16" s="4">
         <v>2025</v>
@@ -2376,19 +2572,20 @@
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
-      <c r="J16" s="13" t="s">
-        <v>65</v>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10" t="s">
+        <v>66</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:11">
       <c r="A17" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D17" s="4">
         <v>2022</v>
@@ -2402,19 +2599,20 @@
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
-      <c r="J17" s="13" t="s">
-        <v>68</v>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10" t="s">
+        <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:11">
       <c r="A18" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B18" s="10" t="s">
         <v>70</v>
       </c>
+      <c r="B18" s="5" t="s">
+        <v>71</v>
+      </c>
       <c r="C18" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D18" s="4">
         <v>2025</v>
@@ -2428,19 +2626,20 @@
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
-      <c r="J18" s="13" t="s">
-        <v>71</v>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10" t="s">
+        <v>72</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:11">
       <c r="A19" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D19" s="4">
         <v>2026</v>
@@ -2449,24 +2648,25 @@
         <v>27</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
-      <c r="J19" s="13" t="s">
-        <v>76</v>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:11">
       <c r="A20" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B20" s="10" t="s">
         <v>78</v>
       </c>
+      <c r="B20" s="5" t="s">
+        <v>79</v>
+      </c>
       <c r="C20" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D20" s="4">
         <v>2021</v>
@@ -2481,24 +2681,25 @@
         <v>12</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I20" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="J20" s="13" t="s">
-        <v>79</v>
+        <v>27</v>
+      </c>
+      <c r="I20" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10" t="s">
+        <v>81</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:11">
       <c r="A21" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>83</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D21" s="4">
         <v>2022</v>
@@ -2512,19 +2713,20 @@
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
-      <c r="J21" s="13" t="s">
-        <v>82</v>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:11">
       <c r="A22" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D22" s="4">
         <v>2026</v>
@@ -2534,19 +2736,22 @@
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
-      <c r="J22" s="13" t="s">
-        <v>86</v>
+      <c r="J22" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="K22" s="10" t="s">
+        <v>89</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:11">
       <c r="A23" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>88</v>
+        <v>90</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>91</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D23" s="4">
         <v>2025</v>
@@ -2555,13 +2760,14 @@
         <v>65</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
-      <c r="J23" s="13" t="s">
-        <v>91</v>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="24" spans="3:10">
@@ -2576,20 +2782,23 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="J2" r:id="rId1" display="https://doi.org/10.1016/j.foodhyd.2018.10.027"/>
-    <hyperlink ref="J3" r:id="rId2" display="https://doi.org/10.1016/j.foodhyd.2020.105926" tooltip="https://doi.org/10.1016/j.foodhyd.2020.105926"/>
-    <hyperlink ref="J5" r:id="rId3" display="https://doi.org/10.1016/j.foodhyd.2024.110605" tooltip="https://doi.org/10.1016/j.foodhyd.2024.110605"/>
-    <hyperlink ref="J6" r:id="rId4" display="https://doi.org/10.1016/j.ijbiomac.2026.150961" tooltip="https://doi.org/10.1016/j.ijbiomac.2026.150961"/>
-    <hyperlink ref="J7" r:id="rId5" display="https://doi.org/10.1016/j.ijbiomac.2023.123414" tooltip="https://doi.org/10.1016/j.ijbiomac.2023.123414"/>
-    <hyperlink ref="J8" r:id="rId6" display="https://doi.org/10.1016/j.foodhyd.2024.110760" tooltip="https://doi.org/10.1016/j.foodhyd.2024.110760"/>
-    <hyperlink ref="J10" r:id="rId7" display="https://doi.org/10.1016/j.foodchem.2021.131612" tooltip="https://doi.org/10.1016/j.foodchem.2021.131612"/>
-    <hyperlink ref="J11" r:id="rId8" display="https://doi.org/10.1016/j.foodhyd.2024.109768" tooltip="https://doi.org/10.1016/j.foodhyd.2024.109768"/>
-    <hyperlink ref="J12" r:id="rId9" display="https://doi.org/10.1016/j.foodchem.2025.145995" tooltip="https://doi.org/10.1016/j.foodchem.2025.145995"/>
-    <hyperlink ref="J14" r:id="rId10" display="https://doi.org/10.1016/j.foodhyd.2025.111778" tooltip="https://doi.org/10.1016/j.foodhyd.2025.111778"/>
-    <hyperlink ref="J16" r:id="rId11" display="https://doi.org/10.1016/j.foodhyd.2024.110696" tooltip="https://doi.org/10.1016/j.foodhyd.2024.110696"/>
-    <hyperlink ref="J17" r:id="rId12" display="https://doi.org/10.1016/j.foodhyd.2022.107876" tooltip="https://doi.org/10.1016/j.foodhyd.2022.107876"/>
-    <hyperlink ref="J20" r:id="rId13" display="https://doi.org/10.1016/j.foodhyd.2021.106906" tooltip="https://doi.org/10.1016/j.foodhyd.2021.106906"/>
-    <hyperlink ref="J21" r:id="rId14" display="https://doi.org/10.1016/j.foodhyd.2022.108022" tooltip="https://doi.org/10.1016/j.foodhyd.2022.108022"/>
+    <hyperlink ref="K2" r:id="rId1" display="https://doi.org/10.1016/j.foodhyd.2018.10.027"/>
+    <hyperlink ref="K3" r:id="rId2" display="https://doi.org/10.1016/j.foodhyd.2020.105926" tooltip="https://doi.org/10.1016/j.foodhyd.2020.105926"/>
+    <hyperlink ref="K5" r:id="rId3" display="https://doi.org/10.1016/j.foodhyd.2024.110605" tooltip="https://doi.org/10.1016/j.foodhyd.2024.110605"/>
+    <hyperlink ref="K6" r:id="rId4" display="https://doi.org/10.1016/j.ijbiomac.2026.150961" tooltip="https://doi.org/10.1016/j.ijbiomac.2026.150961"/>
+    <hyperlink ref="K7" r:id="rId5" display="https://doi.org/10.1016/j.ijbiomac.2023.123414" tooltip="https://doi.org/10.1016/j.ijbiomac.2023.123414"/>
+    <hyperlink ref="K8" r:id="rId6" display="https://doi.org/10.1016/j.foodhyd.2024.110760" tooltip="https://doi.org/10.1016/j.foodhyd.2024.110760"/>
+    <hyperlink ref="K10" r:id="rId7" display="https://doi.org/10.1016/j.foodchem.2021.131612" tooltip="https://doi.org/10.1016/j.foodchem.2021.131612"/>
+    <hyperlink ref="K11" r:id="rId8" display="https://doi.org/10.1016/j.foodhyd.2024.109768" tooltip="https://doi.org/10.1016/j.foodhyd.2024.109768"/>
+    <hyperlink ref="K12" r:id="rId9" display="https://doi.org/10.1016/j.foodchem.2025.145995" tooltip="https://doi.org/10.1016/j.foodchem.2025.145995"/>
+    <hyperlink ref="K14" r:id="rId10" display="https://doi.org/10.1016/j.foodhyd.2025.111778" tooltip="https://doi.org/10.1016/j.foodhyd.2025.111778"/>
+    <hyperlink ref="K16" r:id="rId11" display="https://doi.org/10.1016/j.foodhyd.2024.110696" tooltip="https://doi.org/10.1016/j.foodhyd.2024.110696"/>
+    <hyperlink ref="K17" r:id="rId12" display="https://doi.org/10.1016/j.foodhyd.2022.107876" tooltip="https://doi.org/10.1016/j.foodhyd.2022.107876"/>
+    <hyperlink ref="K20" r:id="rId13" display="https://doi.org/10.1016/j.foodhyd.2021.106906" tooltip="https://doi.org/10.1016/j.foodhyd.2021.106906"/>
+    <hyperlink ref="K21" r:id="rId14" display="https://doi.org/10.1016/j.foodhyd.2022.108022" tooltip="https://doi.org/10.1016/j.foodhyd.2022.108022"/>
+    <hyperlink ref="J4" r:id="rId15" display="https://doi.org/10.1038/s41538-025-00703-5"/>
+    <hyperlink ref="K4" r:id="rId15" display="https://doi.org/10.1038/s41538-025-00703-5"/>
+    <hyperlink ref="J22" r:id="rId16" display="https://doi.org/10.1021/acs.jpcb.5c06919"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/frontend-react/public/data/references_template.xlsx
+++ b/frontend-react/public/data/references_template.xlsx
@@ -893,6 +893,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>Chengzhi Liu, Nan Lv, Yongquan Xu*, Huafei Tong, Yulu Sun, Min Huang, Gerui Ren, Ruibo Wu, Binju Wang, Zexing Cao, </t>
     </r>
     <r>
@@ -985,7 +991,7 @@
     </r>
   </si>
   <si>
-    <t>Critical Reviews in Food Science and Nutrition.</t>
+    <t>Critical Reviews in Food Science and Nutrition</t>
   </si>
   <si>
     <t>8974-8989</t>
@@ -1213,16 +1219,16 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>

--- a/frontend-react/public/data/references_template.xlsx
+++ b/frontend-react/public/data/references_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11520"/>
+    <workbookView windowWidth="28800" windowHeight="13660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="96">
   <si>
     <t>Title</t>
   </si>
@@ -959,6 +959,9 @@
   </si>
   <si>
     <t>Journal of Physical Chemistry B</t>
+  </si>
+  <si>
+    <t>2908-2923</t>
   </si>
   <si>
     <t>https://doi.org/10.1021/acs.jpcb.5c06919</t>
@@ -1224,15 +1227,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
+      <i/>
+      <sz val="10.5"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
-      <i/>
-      <sz val="10.5"/>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
@@ -2737,27 +2740,31 @@
       <c r="D22" s="4">
         <v>2026</v>
       </c>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
+      <c r="E22" s="4">
+        <v>130</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>88</v>
+      </c>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
       <c r="J22" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D23" s="4">
         <v>2025</v>
@@ -2766,14 +2773,14 @@
         <v>65</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
       <c r="J23" s="10"/>
       <c r="K23" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="3:10">

--- a/frontend-react/public/data/references_template.xlsx
+++ b/frontend-react/public/data/references_template.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="95">
   <si>
     <t>Title</t>
   </si>
@@ -962,9 +962,6 @@
   </si>
   <si>
     <t>2908-2923</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1021/acs.jpcb.5c06919</t>
   </si>
   <si>
     <t>https://pubs.acs.org/doi/10.1021/acs.jpcb.5c06919</t>
@@ -2749,22 +2746,20 @@
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
-      <c r="J22" s="12" t="s">
+      <c r="J22" s="12"/>
+      <c r="K22" s="10" t="s">
         <v>89</v>
-      </c>
-      <c r="K22" s="10" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B23" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="C23" s="4" t="s">
         <v>92</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>93</v>
       </c>
       <c r="D23" s="4">
         <v>2025</v>
@@ -2773,14 +2768,14 @@
         <v>65</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
       <c r="J23" s="10"/>
       <c r="K23" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24" spans="3:10">
@@ -2811,7 +2806,6 @@
     <hyperlink ref="K21" r:id="rId14" display="https://doi.org/10.1016/j.foodhyd.2022.108022" tooltip="https://doi.org/10.1016/j.foodhyd.2022.108022"/>
     <hyperlink ref="J4" r:id="rId15" display="https://doi.org/10.1038/s41538-025-00703-5"/>
     <hyperlink ref="K4" r:id="rId15" display="https://doi.org/10.1038/s41538-025-00703-5"/>
-    <hyperlink ref="J22" r:id="rId16" display="https://doi.org/10.1021/acs.jpcb.5c06919"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/frontend-react/public/data/references_template.xlsx
+++ b/frontend-react/public/data/references_template.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="95">
   <si>
     <t>Title</t>
   </si>
@@ -2211,14 +2211,16 @@
       <c r="D4" s="4">
         <v>2026</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
+      <c r="E4" s="4">
+        <v>10</v>
+      </c>
+      <c r="F4" s="4">
+        <v>55</v>
+      </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
-      <c r="J4" s="10" t="s">
-        <v>24</v>
-      </c>
+      <c r="J4" s="10"/>
       <c r="K4" s="10" t="s">
         <v>24</v>
       </c>
@@ -2804,7 +2806,6 @@
     <hyperlink ref="K17" r:id="rId12" display="https://doi.org/10.1016/j.foodhyd.2022.107876" tooltip="https://doi.org/10.1016/j.foodhyd.2022.107876"/>
     <hyperlink ref="K20" r:id="rId13" display="https://doi.org/10.1016/j.foodhyd.2021.106906" tooltip="https://doi.org/10.1016/j.foodhyd.2021.106906"/>
     <hyperlink ref="K21" r:id="rId14" display="https://doi.org/10.1016/j.foodhyd.2022.108022" tooltip="https://doi.org/10.1016/j.foodhyd.2022.108022"/>
-    <hyperlink ref="J4" r:id="rId15" display="https://doi.org/10.1038/s41538-025-00703-5"/>
     <hyperlink ref="K4" r:id="rId15" display="https://doi.org/10.1038/s41538-025-00703-5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
